--- a/2026年度_8月_吹奏楽部活動予定.xlsx
+++ b/2026年度_8月_吹奏楽部活動予定.xlsx
@@ -4106,11 +4106,7 @@
           <t>月</t>
         </is>
       </c>
-      <c r="C10" s="427" t="inlineStr">
-        <is>
-          <t>夏期講習・補習</t>
-        </is>
-      </c>
+      <c r="C10" s="427" t="n"/>
       <c r="D10" s="420" t="inlineStr">
         <is>
           <t>9:00～16:00</t>
@@ -4131,7 +4127,7 @@
       </c>
       <c r="C11" s="430" t="inlineStr">
         <is>
-          <t>夏期講習・補習</t>
+          <t>オフィス改善（～8/8）</t>
         </is>
       </c>
       <c r="D11" s="423" t="inlineStr">
@@ -4152,11 +4148,7 @@
           <t>水</t>
         </is>
       </c>
-      <c r="C12" s="429" t="inlineStr">
-        <is>
-          <t>夏期講習・補習</t>
-        </is>
-      </c>
+      <c r="C12" s="429" t="n"/>
       <c r="D12" s="422" t="inlineStr">
         <is>
           <t>9:00～16:00</t>
@@ -4189,11 +4181,7 @@
           <t>木</t>
         </is>
       </c>
-      <c r="C13" s="427" t="inlineStr">
-        <is>
-          <t>夏期講習・補習</t>
-        </is>
-      </c>
+      <c r="C13" s="427" t="n"/>
       <c r="D13" s="420" t="inlineStr">
         <is>
           <t>9:00～16:00</t>
@@ -4234,7 +4222,7 @@
       </c>
       <c r="C14" s="427" t="inlineStr">
         <is>
-          <t>夏期講習・補習</t>
+          <t>公私合同説明会（専修大学）</t>
         </is>
       </c>
       <c r="D14" s="420" t="inlineStr">
@@ -4365,11 +4353,7 @@
           <t>月</t>
         </is>
       </c>
-      <c r="C17" s="427" t="inlineStr">
-        <is>
-          <t>夏期講習・補習</t>
-        </is>
-      </c>
+      <c r="C17" s="427" t="n"/>
       <c r="D17" s="420" t="inlineStr">
         <is>
           <t>9:00～16:00</t>
@@ -4680,14 +4664,10 @@
           <t>火</t>
         </is>
       </c>
-      <c r="C25" s="430" t="inlineStr">
-        <is>
-          <t>夏期講習・補習</t>
-        </is>
-      </c>
+      <c r="C25" s="430" t="n"/>
       <c r="D25" s="423" t="inlineStr">
         <is>
-          <t>9:00～16:00</t>
+          <t>休み</t>
         </is>
       </c>
       <c r="E25" s="423" t="n"/>
@@ -4740,7 +4720,7 @@
       </c>
       <c r="C27" s="430" t="inlineStr">
         <is>
-          <t>夏期講習・補習　転編入学者選抜</t>
+          <t>夏期講習・補習</t>
         </is>
       </c>
       <c r="D27" s="423" t="inlineStr">
@@ -4824,7 +4804,7 @@
       </c>
       <c r="C31" s="427" t="inlineStr">
         <is>
-          <t>夏期講習・補習</t>
+          <t>夏期講習・補習　（職員健康診断）　校内人権研修PM</t>
         </is>
       </c>
       <c r="D31" s="421" t="inlineStr">
@@ -4847,7 +4827,7 @@
       </c>
       <c r="C32" s="430" t="inlineStr">
         <is>
-          <t>夏期講習・補習</t>
+          <t>夏期講習・補習　シューター訓練</t>
         </is>
       </c>
       <c r="D32" s="423" t="inlineStr">
@@ -4893,7 +4873,7 @@
       </c>
       <c r="C34" s="427" t="inlineStr">
         <is>
-          <t>２学期始業式＋45×6　職員会議</t>
+          <t>２学期始業式（40×6）　職員会議</t>
         </is>
       </c>
       <c r="D34" s="420" t="inlineStr">
@@ -4916,7 +4896,7 @@
       </c>
       <c r="C35" s="427" t="inlineStr">
         <is>
-          <t>第１回推薦願締切　SC来校</t>
+          <t>1,2年：外部試験（全日）　3年：午前授業　SSW</t>
         </is>
       </c>
       <c r="D35" s="420" t="inlineStr">
@@ -4937,7 +4917,11 @@
           <t>土</t>
         </is>
       </c>
-      <c r="C36" s="428" t="n"/>
+      <c r="C36" s="428" t="inlineStr">
+        <is>
+          <t>PTA役員会（AM）</t>
+        </is>
+      </c>
       <c r="D36" s="421" t="inlineStr">
         <is>
           <t>9:00～16:00</t>
@@ -4975,7 +4959,11 @@
           <t>月</t>
         </is>
       </c>
-      <c r="C38" s="428" t="n"/>
+      <c r="C38" s="428" t="inlineStr">
+        <is>
+          <t>第１回推薦願締切　SC</t>
+        </is>
+      </c>
       <c r="D38" s="421" t="inlineStr">
         <is>
           <t>～18:00</t>
@@ -4992,7 +4980,7 @@
     <row r="39" ht="126.75" customHeight="1" thickBot="1">
       <c r="A39" s="524" t="inlineStr">
         <is>
-          <t>※9月の文化祭に向けて練習（要確認）</t>
+          <t>学年会（火）、蔵書点検、プール水質検査・ダニアレルゲン検査、衛生委員会、転編入学者選抜</t>
         </is>
       </c>
       <c r="B39" s="525" t="n"/>

--- a/2026年度_8月_吹奏楽部活動予定.xlsx
+++ b/2026年度_8月_吹奏楽部活動予定.xlsx
@@ -4484,10 +4484,14 @@
       </c>
       <c r="D20" s="420" t="inlineStr">
         <is>
-          <t>休み</t>
-        </is>
-      </c>
-      <c r="E20" s="420" t="n"/>
+          <t>本番（要確認）</t>
+        </is>
+      </c>
+      <c r="E20" s="420" t="inlineStr">
+        <is>
+          <t>神奈川県吹奏楽コンクール 高校B部門 カルッツかわさき</t>
+        </is>
+      </c>
       <c r="F20" s="310" t="n"/>
       <c r="G20" s="310" t="n"/>
       <c r="M20" s="328">
@@ -4767,10 +4771,14 @@
       <c r="C29" s="428" t="n"/>
       <c r="D29" s="421" t="inlineStr">
         <is>
-          <t>9:00～16:00</t>
-        </is>
-      </c>
-      <c r="E29" s="421" t="n"/>
+          <t>13:00～19:00</t>
+        </is>
+      </c>
+      <c r="E29" s="421" t="inlineStr">
+        <is>
+          <t>麻生老人福祉センター夏祭り</t>
+        </is>
+      </c>
       <c r="F29" s="310" t="n"/>
       <c r="G29" s="310" t="n"/>
     </row>

--- a/2026年度_8月_吹奏楽部活動予定.xlsx
+++ b/2026年度_8月_吹奏楽部活動予定.xlsx
@@ -441,7 +441,7 @@
       <sz val="20"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -511,6 +511,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFCC99"/>
+        <bgColor rgb="00FFCC99"/>
       </patternFill>
     </fill>
   </fills>
@@ -1878,7 +1884,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="573">
+  <cellXfs count="585">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
@@ -3542,6 +3548,40 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="54" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="50" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="13" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="3" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -4048,54 +4088,76 @@
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="461" t="n">
+      <c r="A8" s="573" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="461" t="inlineStr">
+      <c r="B8" s="573" t="inlineStr">
         <is>
           <t>土</t>
         </is>
       </c>
-      <c r="C8" s="428" t="n"/>
-      <c r="D8" s="421" t="inlineStr">
+      <c r="C8" s="574" t="n"/>
+      <c r="D8" s="575" t="inlineStr">
         <is>
           <t>9:00～16:00</t>
         </is>
       </c>
-      <c r="E8" s="421" t="inlineStr">
+      <c r="E8" s="575" t="inlineStr">
         <is>
           <t>コンクール後最初の練習</t>
         </is>
       </c>
-      <c r="F8" s="310" t="inlineStr">
+      <c r="F8" s="576" t="inlineStr">
         <is>
           <t>１行  15.75</t>
         </is>
       </c>
-      <c r="G8" s="310" t="n"/>
+      <c r="G8" s="576" t="n"/>
+      <c r="H8" s="577" t="n"/>
+      <c r="I8" s="577" t="n"/>
+      <c r="J8" s="577" t="n"/>
+      <c r="K8" s="577" t="n"/>
+      <c r="L8" s="577" t="n"/>
+      <c r="M8" s="577" t="n"/>
+      <c r="N8" s="577" t="n"/>
+      <c r="O8" s="577" t="n"/>
+      <c r="P8" s="577" t="n"/>
+      <c r="Q8" s="577" t="n"/>
+      <c r="R8" s="577" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="461" t="n">
+      <c r="A9" s="573" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="461" t="inlineStr">
+      <c r="B9" s="573" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C9" s="427" t="n"/>
-      <c r="D9" s="420" t="inlineStr">
+      <c r="C9" s="578" t="n"/>
+      <c r="D9" s="579" t="inlineStr">
         <is>
           <t>休み</t>
         </is>
       </c>
-      <c r="E9" s="420" t="n"/>
-      <c r="F9" s="310" t="inlineStr">
+      <c r="E9" s="579" t="n"/>
+      <c r="F9" s="576" t="inlineStr">
         <is>
           <t>MSPゴシック１２　日・曜日・行事</t>
         </is>
       </c>
-      <c r="G9" s="310" t="n"/>
+      <c r="G9" s="576" t="n"/>
+      <c r="H9" s="577" t="n"/>
+      <c r="I9" s="577" t="n"/>
+      <c r="J9" s="577" t="n"/>
+      <c r="K9" s="577" t="n"/>
+      <c r="L9" s="577" t="n"/>
+      <c r="M9" s="577" t="n"/>
+      <c r="N9" s="577" t="n"/>
+      <c r="O9" s="577" t="n"/>
+      <c r="P9" s="577" t="n"/>
+      <c r="Q9" s="577" t="n"/>
+      <c r="R9" s="577" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="461" t="n">
@@ -4117,45 +4179,45 @@
       <c r="G10" s="310" t="n"/>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="462" t="n">
+      <c r="A11" s="461" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="462" t="inlineStr">
+      <c r="B11" s="461" t="inlineStr">
         <is>
           <t>火</t>
         </is>
       </c>
-      <c r="C11" s="430" t="inlineStr">
+      <c r="C11" s="427" t="inlineStr">
         <is>
           <t>オフィス改善（～8/8）</t>
         </is>
       </c>
-      <c r="D11" s="423" t="inlineStr">
+      <c r="D11" s="420" t="inlineStr">
         <is>
           <t>9:00～16:00</t>
         </is>
       </c>
-      <c r="E11" s="423" t="n"/>
+      <c r="E11" s="420" t="n"/>
       <c r="F11" s="310" t="n"/>
       <c r="G11" s="310" t="n"/>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="462" t="n">
+      <c r="A12" s="461" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="462" t="inlineStr">
+      <c r="B12" s="461" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
-      <c r="C12" s="429" t="n"/>
-      <c r="D12" s="422" t="inlineStr">
+      <c r="C12" s="428" t="n"/>
+      <c r="D12" s="421" t="inlineStr">
         <is>
           <t>9:00～16:00</t>
         </is>
       </c>
-      <c r="E12" s="422" t="n"/>
-      <c r="F12" s="311" t="n"/>
+      <c r="E12" s="421" t="n"/>
+      <c r="F12" s="580" t="n"/>
       <c r="G12" s="310" t="n"/>
       <c r="N12" s="328">
         <f>TIME(9,10,0)</f>
@@ -4188,7 +4250,7 @@
         </is>
       </c>
       <c r="E13" s="420" t="n"/>
-      <c r="F13" s="312" t="inlineStr">
+      <c r="F13" s="581" t="inlineStr">
         <is>
           <t>筬島　勇貴</t>
         </is>
@@ -4231,7 +4293,7 @@
         </is>
       </c>
       <c r="E14" s="420" t="n"/>
-      <c r="F14" s="312" t="inlineStr">
+      <c r="F14" s="581" t="inlineStr">
         <is>
           <t>篠崎　倫也</t>
         </is>
@@ -4265,82 +4327,94 @@
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="461" t="n">
+      <c r="A15" s="573" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="461" t="inlineStr">
+      <c r="B15" s="573" t="inlineStr">
         <is>
           <t>土</t>
         </is>
       </c>
-      <c r="C15" s="428" t="n"/>
-      <c r="D15" s="420" t="inlineStr">
+      <c r="C15" s="574" t="n"/>
+      <c r="D15" s="579" t="inlineStr">
         <is>
           <t>9:00～16:00</t>
         </is>
       </c>
-      <c r="E15" s="421" t="n"/>
-      <c r="F15" s="312" t="inlineStr">
+      <c r="E15" s="575" t="n"/>
+      <c r="F15" s="582" t="inlineStr">
         <is>
           <t>市岡　裕次</t>
         </is>
       </c>
-      <c r="G15" s="310" t="n"/>
-      <c r="M15" s="328">
+      <c r="G15" s="576" t="n"/>
+      <c r="H15" s="577" t="n"/>
+      <c r="I15" s="577" t="n"/>
+      <c r="J15" s="577" t="n"/>
+      <c r="K15" s="577" t="n"/>
+      <c r="L15" s="577" t="n"/>
+      <c r="M15" s="583">
         <f>TIME(0,35,0)</f>
         <v/>
       </c>
-      <c r="N15" s="328">
+      <c r="N15" s="583">
         <f>N14+M15</f>
         <v/>
       </c>
-      <c r="P15" s="328">
+      <c r="O15" s="577" t="n"/>
+      <c r="P15" s="583">
         <f>TIME(0,40,0)</f>
         <v/>
       </c>
-      <c r="Q15" s="328">
+      <c r="Q15" s="583">
         <f>Q14+P15</f>
         <v/>
       </c>
+      <c r="R15" s="577" t="n"/>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="461" t="n">
+      <c r="A16" s="573" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="461" t="inlineStr">
+      <c r="B16" s="573" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C16" s="428" t="n"/>
-      <c r="D16" s="420" t="inlineStr">
+      <c r="C16" s="574" t="n"/>
+      <c r="D16" s="579" t="inlineStr">
         <is>
           <t>休み</t>
         </is>
       </c>
-      <c r="E16" s="421" t="n"/>
-      <c r="F16" s="310" t="n"/>
-      <c r="G16" s="310" t="n"/>
-      <c r="M16" s="328">
+      <c r="E16" s="575" t="n"/>
+      <c r="F16" s="576" t="n"/>
+      <c r="G16" s="576" t="n"/>
+      <c r="H16" s="577" t="n"/>
+      <c r="I16" s="577" t="n"/>
+      <c r="J16" s="577" t="n"/>
+      <c r="K16" s="577" t="n"/>
+      <c r="L16" s="577" t="n"/>
+      <c r="M16" s="583">
         <f>TIME(0,10,0)</f>
         <v/>
       </c>
-      <c r="N16" s="328">
+      <c r="N16" s="583">
         <f>N15+M16</f>
         <v/>
       </c>
-      <c r="O16" s="1" t="n">
+      <c r="O16" s="584" t="n">
         <v>3</v>
       </c>
-      <c r="P16" s="328">
+      <c r="P16" s="583">
         <f>TIME(0,10,0)</f>
         <v/>
       </c>
-      <c r="Q16" s="328">
+      <c r="Q16" s="583">
         <f>Q15+P16</f>
         <v/>
       </c>
-      <c r="R16" s="1" t="n">
+      <c r="R16" s="584" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4380,70 +4454,75 @@
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="462" t="n">
+      <c r="A18" s="573" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="462" t="inlineStr">
+      <c r="B18" s="573" t="inlineStr">
         <is>
           <t>火</t>
         </is>
       </c>
-      <c r="C18" s="430" t="inlineStr">
+      <c r="C18" s="578" t="inlineStr">
         <is>
           <t>山の日</t>
         </is>
       </c>
-      <c r="D18" s="423" t="inlineStr">
+      <c r="D18" s="579" t="inlineStr">
         <is>
           <t>休み</t>
         </is>
       </c>
-      <c r="E18" s="423" t="n"/>
-      <c r="F18" s="310" t="n"/>
-      <c r="G18" s="310" t="n"/>
-      <c r="M18" s="328">
+      <c r="E18" s="579" t="n"/>
+      <c r="F18" s="576" t="n"/>
+      <c r="G18" s="576" t="n"/>
+      <c r="H18" s="577" t="n"/>
+      <c r="I18" s="577" t="n"/>
+      <c r="J18" s="577" t="n"/>
+      <c r="K18" s="577" t="n"/>
+      <c r="L18" s="577" t="n"/>
+      <c r="M18" s="583">
         <f>TIME(0,10,0)</f>
         <v/>
       </c>
-      <c r="N18" s="328">
+      <c r="N18" s="583">
         <f>N17+M18</f>
         <v/>
       </c>
-      <c r="O18" s="1" t="n">
+      <c r="O18" s="584" t="n">
         <v>4</v>
       </c>
-      <c r="P18" s="328">
+      <c r="P18" s="583">
         <f>TIME(0,10,0)</f>
         <v/>
       </c>
-      <c r="Q18" s="328">
+      <c r="Q18" s="583">
         <f>Q17+P18</f>
         <v/>
       </c>
-      <c r="R18" s="1" t="n">
+      <c r="R18" s="584" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="462" t="n">
+      <c r="A19" s="461" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="462" t="inlineStr">
+      <c r="B19" s="461" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
-      <c r="C19" s="429" t="inlineStr">
+      <c r="C19" s="428" t="inlineStr">
         <is>
           <t>学校閉庁日</t>
         </is>
       </c>
-      <c r="D19" s="422" t="inlineStr">
+      <c r="D19" s="421" t="inlineStr">
         <is>
           <t>休み</t>
         </is>
       </c>
-      <c r="E19" s="422" t="n"/>
+      <c r="E19" s="421" t="n"/>
       <c r="F19" s="310" t="n"/>
       <c r="G19" s="310" t="n"/>
       <c r="M19" s="328">
@@ -4557,73 +4636,87 @@
       </c>
     </row>
     <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="461" t="n">
+      <c r="A22" s="573" t="n">
         <v>15</v>
       </c>
-      <c r="B22" s="461" t="inlineStr">
+      <c r="B22" s="573" t="inlineStr">
         <is>
           <t>土</t>
         </is>
       </c>
-      <c r="C22" s="428" t="n"/>
-      <c r="D22" s="420" t="inlineStr">
+      <c r="C22" s="574" t="n"/>
+      <c r="D22" s="579" t="inlineStr">
         <is>
           <t>休み</t>
         </is>
       </c>
-      <c r="E22" s="421" t="n"/>
-      <c r="F22" s="310" t="n"/>
-      <c r="G22" s="310" t="n"/>
-      <c r="M22" s="328">
+      <c r="E22" s="575" t="n"/>
+      <c r="F22" s="576" t="n"/>
+      <c r="G22" s="576" t="n"/>
+      <c r="H22" s="577" t="n"/>
+      <c r="I22" s="577" t="n"/>
+      <c r="J22" s="577" t="n"/>
+      <c r="K22" s="577" t="n"/>
+      <c r="L22" s="577" t="n"/>
+      <c r="M22" s="583">
         <f>TIME(0,5,0)</f>
         <v/>
       </c>
-      <c r="N22" s="328">
+      <c r="N22" s="583">
         <f>N21+M22</f>
         <v/>
       </c>
-      <c r="P22" s="328">
+      <c r="O22" s="577" t="n"/>
+      <c r="P22" s="583">
         <f>TIME(0,10,0)</f>
         <v/>
       </c>
-      <c r="Q22" s="328">
+      <c r="Q22" s="583">
         <f>Q21+P22</f>
         <v/>
       </c>
-      <c r="R22" s="1" t="n">
+      <c r="R22" s="584" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="461" t="n">
+      <c r="A23" s="573" t="n">
         <v>16</v>
       </c>
-      <c r="B23" s="461" t="inlineStr">
+      <c r="B23" s="573" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C23" s="427" t="n"/>
-      <c r="D23" s="420" t="inlineStr">
+      <c r="C23" s="578" t="n"/>
+      <c r="D23" s="579" t="inlineStr">
         <is>
           <t>休み</t>
         </is>
       </c>
-      <c r="E23" s="421" t="n"/>
-      <c r="F23" s="310" t="n"/>
-      <c r="G23" s="310" t="n"/>
-      <c r="M23" s="328">
+      <c r="E23" s="575" t="n"/>
+      <c r="F23" s="576" t="n"/>
+      <c r="G23" s="576" t="n"/>
+      <c r="H23" s="577" t="n"/>
+      <c r="I23" s="577" t="n"/>
+      <c r="J23" s="577" t="n"/>
+      <c r="K23" s="577" t="n"/>
+      <c r="L23" s="577" t="n"/>
+      <c r="M23" s="583">
         <f>TIME(0,35,0)</f>
         <v/>
       </c>
-      <c r="P23" s="328">
+      <c r="N23" s="577" t="n"/>
+      <c r="O23" s="577" t="n"/>
+      <c r="P23" s="583">
         <f>TIME(0,40,0)</f>
         <v/>
       </c>
-      <c r="Q23" s="328">
+      <c r="Q23" s="583">
         <f>Q22+P23</f>
         <v/>
       </c>
+      <c r="R23" s="577" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1">
       <c r="A24" s="461" t="n">
@@ -4660,21 +4753,21 @@
       </c>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="462" t="n">
+      <c r="A25" s="461" t="n">
         <v>18</v>
       </c>
-      <c r="B25" s="462" t="inlineStr">
+      <c r="B25" s="461" t="inlineStr">
         <is>
           <t>火</t>
         </is>
       </c>
-      <c r="C25" s="430" t="n"/>
-      <c r="D25" s="423" t="inlineStr">
+      <c r="C25" s="427" t="n"/>
+      <c r="D25" s="420" t="inlineStr">
         <is>
           <t>休み</t>
         </is>
       </c>
-      <c r="E25" s="423" t="n"/>
+      <c r="E25" s="420" t="n"/>
       <c r="F25" s="310" t="n"/>
       <c r="G25" s="310" t="n"/>
       <c r="M25" s="328">
@@ -4691,48 +4784,48 @@
       </c>
     </row>
     <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="462" t="n">
+      <c r="A26" s="461" t="n">
         <v>19</v>
       </c>
-      <c r="B26" s="462" t="inlineStr">
+      <c r="B26" s="461" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
-      <c r="C26" s="429" t="inlineStr">
+      <c r="C26" s="428" t="inlineStr">
         <is>
           <t>夏期講習・補習</t>
         </is>
       </c>
-      <c r="D26" s="422" t="inlineStr">
+      <c r="D26" s="421" t="inlineStr">
         <is>
           <t>9:00～16:00</t>
         </is>
       </c>
-      <c r="E26" s="422" t="n"/>
+      <c r="E26" s="421" t="n"/>
       <c r="F26" s="310" t="n"/>
       <c r="G26" s="310" t="n"/>
     </row>
     <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="462" t="n">
+      <c r="A27" s="461" t="n">
         <v>20</v>
       </c>
-      <c r="B27" s="462" t="inlineStr">
+      <c r="B27" s="461" t="inlineStr">
         <is>
           <t>木</t>
         </is>
       </c>
-      <c r="C27" s="430" t="inlineStr">
+      <c r="C27" s="427" t="inlineStr">
         <is>
           <t>夏期講習・補習</t>
         </is>
       </c>
-      <c r="D27" s="423" t="inlineStr">
+      <c r="D27" s="420" t="inlineStr">
         <is>
           <t>9:00～16:00</t>
         </is>
       </c>
-      <c r="E27" s="423" t="n"/>
+      <c r="E27" s="420" t="n"/>
       <c r="F27" s="310" t="n"/>
       <c r="G27" s="310" t="n"/>
     </row>
@@ -4760,46 +4853,68 @@
       <c r="G28" s="310" t="n"/>
     </row>
     <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="461" t="n">
+      <c r="A29" s="573" t="n">
         <v>22</v>
       </c>
-      <c r="B29" s="461" t="inlineStr">
+      <c r="B29" s="573" t="inlineStr">
         <is>
           <t>土</t>
         </is>
       </c>
-      <c r="C29" s="428" t="n"/>
-      <c r="D29" s="421" t="inlineStr">
+      <c r="C29" s="574" t="n"/>
+      <c r="D29" s="575" t="inlineStr">
         <is>
           <t>13:00～19:00</t>
         </is>
       </c>
-      <c r="E29" s="421" t="inlineStr">
+      <c r="E29" s="575" t="inlineStr">
         <is>
           <t>麻生老人福祉センター夏祭り</t>
         </is>
       </c>
-      <c r="F29" s="310" t="n"/>
-      <c r="G29" s="310" t="n"/>
+      <c r="F29" s="576" t="n"/>
+      <c r="G29" s="576" t="n"/>
+      <c r="H29" s="577" t="n"/>
+      <c r="I29" s="577" t="n"/>
+      <c r="J29" s="577" t="n"/>
+      <c r="K29" s="577" t="n"/>
+      <c r="L29" s="577" t="n"/>
+      <c r="M29" s="577" t="n"/>
+      <c r="N29" s="577" t="n"/>
+      <c r="O29" s="577" t="n"/>
+      <c r="P29" s="577" t="n"/>
+      <c r="Q29" s="577" t="n"/>
+      <c r="R29" s="577" t="n"/>
     </row>
     <row r="30" ht="23.4" customHeight="1">
-      <c r="A30" s="461" t="n">
+      <c r="A30" s="573" t="n">
         <v>23</v>
       </c>
-      <c r="B30" s="461" t="inlineStr">
+      <c r="B30" s="573" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C30" s="428" t="n"/>
-      <c r="D30" s="421" t="inlineStr">
+      <c r="C30" s="574" t="n"/>
+      <c r="D30" s="575" t="inlineStr">
         <is>
           <t>休み</t>
         </is>
       </c>
-      <c r="E30" s="421" t="n"/>
-      <c r="F30" s="310" t="n"/>
-      <c r="G30" s="310" t="n"/>
+      <c r="E30" s="575" t="n"/>
+      <c r="F30" s="576" t="n"/>
+      <c r="G30" s="576" t="n"/>
+      <c r="H30" s="577" t="n"/>
+      <c r="I30" s="577" t="n"/>
+      <c r="J30" s="577" t="n"/>
+      <c r="K30" s="577" t="n"/>
+      <c r="L30" s="577" t="n"/>
+      <c r="M30" s="577" t="n"/>
+      <c r="N30" s="577" t="n"/>
+      <c r="O30" s="577" t="n"/>
+      <c r="P30" s="577" t="n"/>
+      <c r="Q30" s="577" t="n"/>
+      <c r="R30" s="577" t="n"/>
     </row>
     <row r="31" ht="24" customHeight="1">
       <c r="A31" s="461" t="n">
@@ -4825,48 +4940,48 @@
       <c r="G31" s="310" t="n"/>
     </row>
     <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="462" t="n">
+      <c r="A32" s="461" t="n">
         <v>25</v>
       </c>
-      <c r="B32" s="462" t="inlineStr">
+      <c r="B32" s="461" t="inlineStr">
         <is>
           <t>火</t>
         </is>
       </c>
-      <c r="C32" s="430" t="inlineStr">
+      <c r="C32" s="427" t="inlineStr">
         <is>
           <t>夏期講習・補習　シューター訓練</t>
         </is>
       </c>
-      <c r="D32" s="423" t="inlineStr">
+      <c r="D32" s="420" t="inlineStr">
         <is>
           <t>9:00～16:00</t>
         </is>
       </c>
-      <c r="E32" s="423" t="n"/>
+      <c r="E32" s="420" t="n"/>
       <c r="F32" s="310" t="n"/>
       <c r="G32" s="310" t="n"/>
     </row>
     <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="462" t="n">
+      <c r="A33" s="461" t="n">
         <v>26</v>
       </c>
-      <c r="B33" s="462" t="inlineStr">
+      <c r="B33" s="461" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
-      <c r="C33" s="429" t="inlineStr">
+      <c r="C33" s="428" t="inlineStr">
         <is>
           <t>夏季休業終了</t>
         </is>
       </c>
-      <c r="D33" s="422" t="inlineStr">
+      <c r="D33" s="421" t="inlineStr">
         <is>
           <t>9:00～12:00</t>
         </is>
       </c>
-      <c r="E33" s="422" t="n"/>
+      <c r="E33" s="421" t="n"/>
       <c r="F33" s="310" t="n"/>
       <c r="G33" s="310" t="n"/>
     </row>
@@ -4917,46 +5032,68 @@
       <c r="G35" s="310" t="n"/>
     </row>
     <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="461" t="n">
+      <c r="A36" s="573" t="n">
         <v>29</v>
       </c>
-      <c r="B36" s="461" t="inlineStr">
+      <c r="B36" s="573" t="inlineStr">
         <is>
           <t>土</t>
         </is>
       </c>
-      <c r="C36" s="428" t="inlineStr">
+      <c r="C36" s="574" t="inlineStr">
         <is>
           <t>PTA役員会（AM）</t>
         </is>
       </c>
-      <c r="D36" s="421" t="inlineStr">
+      <c r="D36" s="575" t="inlineStr">
         <is>
           <t>9:00～16:00</t>
         </is>
       </c>
-      <c r="E36" s="421" t="n"/>
-      <c r="F36" s="310" t="n"/>
-      <c r="G36" s="310" t="n"/>
+      <c r="E36" s="575" t="n"/>
+      <c r="F36" s="576" t="n"/>
+      <c r="G36" s="576" t="n"/>
+      <c r="H36" s="577" t="n"/>
+      <c r="I36" s="577" t="n"/>
+      <c r="J36" s="577" t="n"/>
+      <c r="K36" s="577" t="n"/>
+      <c r="L36" s="577" t="n"/>
+      <c r="M36" s="577" t="n"/>
+      <c r="N36" s="577" t="n"/>
+      <c r="O36" s="577" t="n"/>
+      <c r="P36" s="577" t="n"/>
+      <c r="Q36" s="577" t="n"/>
+      <c r="R36" s="577" t="n"/>
     </row>
     <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="461" t="n">
+      <c r="A37" s="573" t="n">
         <v>30</v>
       </c>
-      <c r="B37" s="461" t="inlineStr">
+      <c r="B37" s="573" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C37" s="428" t="n"/>
-      <c r="D37" s="421" t="inlineStr">
+      <c r="C37" s="574" t="n"/>
+      <c r="D37" s="575" t="inlineStr">
         <is>
           <t>休み</t>
         </is>
       </c>
-      <c r="E37" s="421" t="n"/>
-      <c r="F37" s="310" t="n"/>
-      <c r="G37" s="310" t="n"/>
+      <c r="E37" s="575" t="n"/>
+      <c r="F37" s="576" t="n"/>
+      <c r="G37" s="576" t="n"/>
+      <c r="H37" s="577" t="n"/>
+      <c r="I37" s="577" t="n"/>
+      <c r="J37" s="577" t="n"/>
+      <c r="K37" s="577" t="n"/>
+      <c r="L37" s="577" t="n"/>
+      <c r="M37" s="577" t="n"/>
+      <c r="N37" s="577" t="n"/>
+      <c r="O37" s="577" t="n"/>
+      <c r="P37" s="577" t="n"/>
+      <c r="Q37" s="577" t="n"/>
+      <c r="R37" s="577" t="n"/>
     </row>
     <row r="38" ht="24" customHeight="1" thickBot="1">
       <c r="A38" s="463" t="n">

--- a/2026年度_8月_吹奏楽部活動予定.xlsx
+++ b/2026年度_8月_吹奏楽部活動予定.xlsx
@@ -26,6 +26,7 @@
     <sheet name="令和4年度5月 (3)" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="令和６年度1月" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="令和6年度2月 (4)" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="令和８年9月" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'令和８年3月'!$A$7:$E$39</definedName>
@@ -1884,7 +1885,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="585">
+  <cellXfs count="586">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
@@ -3581,6 +3582,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -23357,6 +23361,1178 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr codeName="Sheet1">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:R39"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.2"/>
+  <cols>
+    <col width="6.109375" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
+    <col width="4.88671875" customWidth="1" style="1" min="2" max="2"/>
+    <col width="38.6640625" customWidth="1" style="472" min="3" max="3"/>
+    <col width="12.5546875" customWidth="1" style="1" min="4" max="4"/>
+    <col width="43.6640625" customWidth="1" style="472" min="5" max="5"/>
+    <col width="9" customWidth="1" style="1" min="6" max="12"/>
+    <col width="9.88671875" bestFit="1" customWidth="1" style="1" min="13" max="13"/>
+    <col width="9" customWidth="1" style="1" min="14" max="15"/>
+    <col width="9.88671875" bestFit="1" customWidth="1" style="1" min="16" max="17"/>
+    <col width="9" customWidth="1" style="1" min="18" max="16384"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="27.75" customHeight="1">
+      <c r="A1" s="467" t="inlineStr">
+        <is>
+          <t>【９月・10月（暫定）　行事予定】　１学年・２学年・３学年・管理G・進路G・生徒会G・生活G・入選G</t>
+        </is>
+      </c>
+      <c r="D1" s="329" t="n"/>
+      <c r="E1" s="330" t="n"/>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>加筆・修正は朱書きで、３月７日（火）１５時までにお願いします。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="23.25" customHeight="1" thickBot="1">
+      <c r="A2" s="468" t="inlineStr">
+        <is>
+          <t>夏季休業中に申し訳ございません。加筆・修正は朱書きで、7月30日（金）１７時までにお願いします。</t>
+        </is>
+      </c>
+      <c r="B2" s="522" t="n"/>
+      <c r="C2" s="522" t="n"/>
+      <c r="D2" s="329" t="n"/>
+      <c r="E2" s="330" t="n"/>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>企画会議資料　　5月１２日（木）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="469" t="inlineStr">
+        <is>
+          <t>グループ会議資料（回覧）　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　令和３年７月26日（月）</t>
+        </is>
+      </c>
+      <c r="B3" s="523" t="n"/>
+      <c r="C3" s="523" t="n"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>加筆・修正は朱書きで、３月７日（火）１５時までにお願いします。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="471" t="inlineStr">
+        <is>
+          <t>企画会議資料　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　令和３年８月稟議</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>企画会議資料　　5月１２日（木）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="A5" s="471" t="inlineStr">
+        <is>
+          <t>朝の打ち合わせ資料　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　令和３年８月　日（　）</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customHeight="1" thickBot="1">
+      <c r="A6" s="473" t="inlineStr">
+        <is>
+          <t>学務開発Ｇ</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>企画会議資料　　１０月１３日（木）</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="n"/>
+    </row>
+    <row r="7" ht="24" customHeight="1" thickBot="1">
+      <c r="A7" s="407" t="inlineStr">
+        <is>
+          <t>2026年度　令和8年　9月　吹奏楽部活動予定</t>
+        </is>
+      </c>
+      <c r="B7" s="408" t="n"/>
+      <c r="C7" s="408" t="n"/>
+      <c r="D7" s="408" t="n"/>
+      <c r="E7" s="409" t="n"/>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>←ヒラギノ角ゴPro W3 13Bold</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>企画会議（稟議）資料</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="461" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="461" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C8" s="428" t="inlineStr">
+        <is>
+          <t>40×6</t>
+        </is>
+      </c>
+      <c r="D8" s="421" t="inlineStr">
+        <is>
+          <t>～18:00</t>
+        </is>
+      </c>
+      <c r="E8" s="421" t="n"/>
+      <c r="F8" s="310" t="inlineStr">
+        <is>
+          <t>１行  15.75</t>
+        </is>
+      </c>
+      <c r="G8" s="310" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="461" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="461" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C9" s="427" t="inlineStr">
+        <is>
+          <t>40×6</t>
+        </is>
+      </c>
+      <c r="D9" s="420" t="inlineStr">
+        <is>
+          <t>～18:00</t>
+        </is>
+      </c>
+      <c r="E9" s="420" t="n"/>
+      <c r="F9" s="310" t="inlineStr">
+        <is>
+          <t>MSPゴシック１２　日・曜日・行事</t>
+        </is>
+      </c>
+      <c r="G9" s="310" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="461" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="461" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C10" s="427" t="inlineStr">
+        <is>
+          <t>40×6</t>
+        </is>
+      </c>
+      <c r="D10" s="420" t="inlineStr">
+        <is>
+          <t>～18:00</t>
+        </is>
+      </c>
+      <c r="E10" s="420" t="n"/>
+      <c r="F10" s="310" t="n"/>
+      <c r="G10" s="310" t="n"/>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="461" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="461" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C11" s="427" t="inlineStr">
+        <is>
+          <t>文化祭全日準備①　SSW来校</t>
+        </is>
+      </c>
+      <c r="D11" s="420" t="inlineStr">
+        <is>
+          <t>リハーサル</t>
+        </is>
+      </c>
+      <c r="E11" s="420" t="inlineStr">
+        <is>
+          <t>おそらく合奏はリハの時間のみ</t>
+        </is>
+      </c>
+      <c r="F11" s="310" t="n"/>
+      <c r="G11" s="310" t="n"/>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="573" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="573" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C12" s="574" t="inlineStr">
+        <is>
+          <t>文化祭①</t>
+        </is>
+      </c>
+      <c r="D12" s="575" t="inlineStr">
+        <is>
+          <t>本番</t>
+        </is>
+      </c>
+      <c r="E12" s="575" t="n"/>
+      <c r="F12" s="585" t="n"/>
+      <c r="G12" s="576" t="n"/>
+      <c r="H12" s="577" t="n"/>
+      <c r="I12" s="577" t="n"/>
+      <c r="J12" s="577" t="n"/>
+      <c r="K12" s="577" t="n"/>
+      <c r="L12" s="577" t="n"/>
+      <c r="M12" s="577" t="n"/>
+      <c r="N12" s="583">
+        <f>TIME(9,10,0)</f>
+        <v/>
+      </c>
+      <c r="O12" s="584" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" s="577" t="n"/>
+      <c r="Q12" s="583">
+        <f>TIME(9,0,0)</f>
+        <v/>
+      </c>
+      <c r="R12" s="584" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="573" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="573" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C13" s="578" t="inlineStr">
+        <is>
+          <t>文化祭②</t>
+        </is>
+      </c>
+      <c r="D13" s="579" t="inlineStr">
+        <is>
+          <t>本番</t>
+        </is>
+      </c>
+      <c r="E13" s="579" t="n"/>
+      <c r="F13" s="582" t="inlineStr">
+        <is>
+          <t>筬島　勇貴</t>
+        </is>
+      </c>
+      <c r="G13" s="576" t="n"/>
+      <c r="H13" s="577" t="n"/>
+      <c r="I13" s="577" t="n"/>
+      <c r="J13" s="577" t="n"/>
+      <c r="K13" s="577" t="n"/>
+      <c r="L13" s="577" t="n"/>
+      <c r="M13" s="583">
+        <f>TIME(0,35,0)</f>
+        <v/>
+      </c>
+      <c r="N13" s="583">
+        <f>N12+M13</f>
+        <v/>
+      </c>
+      <c r="O13" s="577" t="n"/>
+      <c r="P13" s="583">
+        <f>TIME(0,40,0)</f>
+        <v/>
+      </c>
+      <c r="Q13" s="583">
+        <f>Q12+P13</f>
+        <v/>
+      </c>
+      <c r="R13" s="577" t="n"/>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="461" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="461" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C14" s="427" t="inlineStr">
+        <is>
+          <t>片付け・LHR</t>
+        </is>
+      </c>
+      <c r="D14" s="420" t="inlineStr">
+        <is>
+          <t>片付け</t>
+        </is>
+      </c>
+      <c r="E14" s="420" t="n"/>
+      <c r="F14" s="581" t="inlineStr">
+        <is>
+          <t>篠崎　倫也</t>
+        </is>
+      </c>
+      <c r="G14" s="310" t="inlineStr">
+        <is>
+          <t>→角田</t>
+        </is>
+      </c>
+      <c r="M14" s="328">
+        <f>TIME(0,10,0)</f>
+        <v/>
+      </c>
+      <c r="N14" s="328">
+        <f>N13+M14</f>
+        <v/>
+      </c>
+      <c r="O14" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="P14" s="328">
+        <f>TIME(0,10,0)</f>
+        <v/>
+      </c>
+      <c r="Q14" s="328">
+        <f>Q13+P14</f>
+        <v/>
+      </c>
+      <c r="R14" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="461" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="461" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C15" s="428" t="inlineStr">
+        <is>
+          <t>代休</t>
+        </is>
+      </c>
+      <c r="D15" s="420" t="inlineStr">
+        <is>
+          <t>休み</t>
+        </is>
+      </c>
+      <c r="E15" s="421" t="n"/>
+      <c r="F15" s="581" t="inlineStr">
+        <is>
+          <t>市岡　裕次</t>
+        </is>
+      </c>
+      <c r="G15" s="310" t="n"/>
+      <c r="M15" s="328">
+        <f>TIME(0,35,0)</f>
+        <v/>
+      </c>
+      <c r="N15" s="328">
+        <f>N14+M15</f>
+        <v/>
+      </c>
+      <c r="P15" s="328">
+        <f>TIME(0,40,0)</f>
+        <v/>
+      </c>
+      <c r="Q15" s="328">
+        <f>Q14+P15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="461" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="461" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C16" s="428" t="inlineStr">
+        <is>
+          <t>代休</t>
+        </is>
+      </c>
+      <c r="D16" s="420" t="inlineStr">
+        <is>
+          <t>休み</t>
+        </is>
+      </c>
+      <c r="E16" s="421" t="n"/>
+      <c r="F16" s="310" t="n"/>
+      <c r="G16" s="310" t="n"/>
+      <c r="M16" s="328">
+        <f>TIME(0,10,0)</f>
+        <v/>
+      </c>
+      <c r="N16" s="328">
+        <f>N15+M16</f>
+        <v/>
+      </c>
+      <c r="O16" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="P16" s="328">
+        <f>TIME(0,10,0)</f>
+        <v/>
+      </c>
+      <c r="Q16" s="328">
+        <f>Q15+P16</f>
+        <v/>
+      </c>
+      <c r="R16" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="461" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="461" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C17" s="427" t="inlineStr">
+        <is>
+          <t>40×6　推薦原案作成会議①　SC来校</t>
+        </is>
+      </c>
+      <c r="D17" s="420" t="inlineStr">
+        <is>
+          <t>～18:00</t>
+        </is>
+      </c>
+      <c r="E17" s="421" t="n"/>
+      <c r="F17" s="310" t="n"/>
+      <c r="G17" s="310" t="n"/>
+      <c r="M17" s="328">
+        <f>TIME(0,35,0)</f>
+        <v/>
+      </c>
+      <c r="N17" s="328">
+        <f>N16+M17</f>
+        <v/>
+      </c>
+      <c r="P17" s="328">
+        <f>TIME(0,40,0)</f>
+        <v/>
+      </c>
+      <c r="Q17" s="328">
+        <f>Q16+P17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="461" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="461" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C18" s="427" t="inlineStr">
+        <is>
+          <t>40×6　推薦原案作成会議②　SSW来校</t>
+        </is>
+      </c>
+      <c r="D18" s="420" t="inlineStr">
+        <is>
+          <t>～18:00</t>
+        </is>
+      </c>
+      <c r="E18" s="420" t="n"/>
+      <c r="F18" s="310" t="n"/>
+      <c r="G18" s="310" t="n"/>
+      <c r="M18" s="328">
+        <f>TIME(0,10,0)</f>
+        <v/>
+      </c>
+      <c r="N18" s="328">
+        <f>N17+M18</f>
+        <v/>
+      </c>
+      <c r="O18" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="P18" s="328">
+        <f>TIME(0,10,0)</f>
+        <v/>
+      </c>
+      <c r="Q18" s="328">
+        <f>Q17+P18</f>
+        <v/>
+      </c>
+      <c r="R18" s="1" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="573" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" s="573" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C19" s="574" t="n"/>
+      <c r="D19" s="575" t="inlineStr">
+        <is>
+          <t>9:00～16:00</t>
+        </is>
+      </c>
+      <c r="E19" s="575" t="n"/>
+      <c r="F19" s="576" t="n"/>
+      <c r="G19" s="576" t="n"/>
+      <c r="H19" s="577" t="n"/>
+      <c r="I19" s="577" t="n"/>
+      <c r="J19" s="577" t="n"/>
+      <c r="K19" s="577" t="n"/>
+      <c r="L19" s="577" t="n"/>
+      <c r="M19" s="583">
+        <f>TIME(0,35,0)</f>
+        <v/>
+      </c>
+      <c r="N19" s="583">
+        <f>N18+M19</f>
+        <v/>
+      </c>
+      <c r="O19" s="577" t="n"/>
+      <c r="P19" s="583">
+        <f>TIME(0,40,0)</f>
+        <v/>
+      </c>
+      <c r="Q19" s="583">
+        <f>Q18+P19</f>
+        <v/>
+      </c>
+      <c r="R19" s="584" t="inlineStr">
+        <is>
+          <t>昼休み</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="23.4" customHeight="1">
+      <c r="A20" s="573" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" s="573" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C20" s="578" t="n"/>
+      <c r="D20" s="579" t="inlineStr">
+        <is>
+          <t>休み</t>
+        </is>
+      </c>
+      <c r="E20" s="579" t="n"/>
+      <c r="F20" s="576" t="n"/>
+      <c r="G20" s="576" t="n"/>
+      <c r="H20" s="577" t="n"/>
+      <c r="I20" s="577" t="n"/>
+      <c r="J20" s="577" t="n"/>
+      <c r="K20" s="577" t="n"/>
+      <c r="L20" s="577" t="n"/>
+      <c r="M20" s="583">
+        <f>TIME(0,10,0)</f>
+        <v/>
+      </c>
+      <c r="N20" s="583">
+        <f>N19+M20</f>
+        <v/>
+      </c>
+      <c r="O20" s="584" t="n">
+        <v>5</v>
+      </c>
+      <c r="P20" s="583">
+        <f>TIME(0,45,0)</f>
+        <v/>
+      </c>
+      <c r="Q20" s="583">
+        <f>Q19+P20</f>
+        <v/>
+      </c>
+      <c r="R20" s="584" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="461" t="n">
+        <v>14</v>
+      </c>
+      <c r="B21" s="461" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C21" s="427" t="n"/>
+      <c r="D21" s="420" t="inlineStr">
+        <is>
+          <t>～18:00</t>
+        </is>
+      </c>
+      <c r="E21" s="420" t="n"/>
+      <c r="F21" s="310" t="n"/>
+      <c r="G21" s="310" t="n"/>
+      <c r="M21" s="328">
+        <f>TIME(0,35,0)</f>
+        <v/>
+      </c>
+      <c r="N21" s="328">
+        <f>N20+M21</f>
+        <v/>
+      </c>
+      <c r="P21" s="328">
+        <f>TIME(0,40,0)</f>
+        <v/>
+      </c>
+      <c r="Q21" s="328">
+        <f>Q20+P21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="461" t="n">
+        <v>15</v>
+      </c>
+      <c r="B22" s="461" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C22" s="428" t="n"/>
+      <c r="D22" s="420" t="inlineStr">
+        <is>
+          <t>～18:00</t>
+        </is>
+      </c>
+      <c r="E22" s="421" t="n"/>
+      <c r="F22" s="310" t="n"/>
+      <c r="G22" s="310" t="n"/>
+      <c r="M22" s="328">
+        <f>TIME(0,5,0)</f>
+        <v/>
+      </c>
+      <c r="N22" s="328">
+        <f>N21+M22</f>
+        <v/>
+      </c>
+      <c r="P22" s="328">
+        <f>TIME(0,10,0)</f>
+        <v/>
+      </c>
+      <c r="Q22" s="328">
+        <f>Q21+P22</f>
+        <v/>
+      </c>
+      <c r="R22" s="1" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="461" t="n">
+        <v>16</v>
+      </c>
+      <c r="B23" s="461" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C23" s="427" t="inlineStr">
+        <is>
+          <t>40×6　第１回推薦会議①</t>
+        </is>
+      </c>
+      <c r="D23" s="420" t="inlineStr">
+        <is>
+          <t>～18:00</t>
+        </is>
+      </c>
+      <c r="E23" s="421" t="n"/>
+      <c r="F23" s="310" t="n"/>
+      <c r="G23" s="310" t="n"/>
+      <c r="M23" s="328">
+        <f>TIME(0,35,0)</f>
+        <v/>
+      </c>
+      <c r="P23" s="328">
+        <f>TIME(0,40,0)</f>
+        <v/>
+      </c>
+      <c r="Q23" s="328">
+        <f>Q22+P23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="461" t="n">
+        <v>17</v>
+      </c>
+      <c r="B24" s="461" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C24" s="427" t="inlineStr">
+        <is>
+          <t>40×6　第１回推薦会議②　SC来校</t>
+        </is>
+      </c>
+      <c r="D24" s="420" t="inlineStr">
+        <is>
+          <t>～18:00</t>
+        </is>
+      </c>
+      <c r="E24" s="420" t="n"/>
+      <c r="F24" s="310" t="n"/>
+      <c r="G24" s="310" t="n"/>
+      <c r="M24" s="328">
+        <f>TIME(0,10,0)</f>
+        <v/>
+      </c>
+      <c r="P24" s="328">
+        <f>TIME(0,10,0)</f>
+        <v/>
+      </c>
+      <c r="Q24" s="328">
+        <f>Q23+P24</f>
+        <v/>
+      </c>
+      <c r="R24" s="1" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="461" t="n">
+        <v>18</v>
+      </c>
+      <c r="B25" s="461" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C25" s="427" t="inlineStr">
+        <is>
+          <t>職員会議　推薦結果通知　SSW来校</t>
+        </is>
+      </c>
+      <c r="D25" s="420" t="inlineStr">
+        <is>
+          <t>～18:00</t>
+        </is>
+      </c>
+      <c r="E25" s="420" t="n"/>
+      <c r="F25" s="310" t="n"/>
+      <c r="G25" s="310" t="n"/>
+      <c r="M25" s="328">
+        <f>TIME(0,35,0)</f>
+        <v/>
+      </c>
+      <c r="P25" s="328">
+        <f>TIME(0,40,0)</f>
+        <v/>
+      </c>
+      <c r="Q25" s="328">
+        <f>Q24+P25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="573" t="n">
+        <v>19</v>
+      </c>
+      <c r="B26" s="573" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C26" s="574" t="n"/>
+      <c r="D26" s="575" t="inlineStr">
+        <is>
+          <t>9:00～16:00</t>
+        </is>
+      </c>
+      <c r="E26" s="575" t="n"/>
+      <c r="F26" s="576" t="n"/>
+      <c r="G26" s="576" t="n"/>
+      <c r="H26" s="577" t="n"/>
+      <c r="I26" s="577" t="n"/>
+      <c r="J26" s="577" t="n"/>
+      <c r="K26" s="577" t="n"/>
+      <c r="L26" s="577" t="n"/>
+      <c r="M26" s="577" t="n"/>
+      <c r="N26" s="577" t="n"/>
+      <c r="O26" s="577" t="n"/>
+      <c r="P26" s="577" t="n"/>
+      <c r="Q26" s="577" t="n"/>
+      <c r="R26" s="577" t="n"/>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="573" t="n">
+        <v>20</v>
+      </c>
+      <c r="B27" s="573" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C27" s="578" t="n"/>
+      <c r="D27" s="579" t="inlineStr">
+        <is>
+          <t>休み</t>
+        </is>
+      </c>
+      <c r="E27" s="579" t="n"/>
+      <c r="F27" s="576" t="n"/>
+      <c r="G27" s="576" t="n"/>
+      <c r="H27" s="577" t="n"/>
+      <c r="I27" s="577" t="n"/>
+      <c r="J27" s="577" t="n"/>
+      <c r="K27" s="577" t="n"/>
+      <c r="L27" s="577" t="n"/>
+      <c r="M27" s="577" t="n"/>
+      <c r="N27" s="577" t="n"/>
+      <c r="O27" s="577" t="n"/>
+      <c r="P27" s="577" t="n"/>
+      <c r="Q27" s="577" t="n"/>
+      <c r="R27" s="577" t="n"/>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="573" t="n">
+        <v>21</v>
+      </c>
+      <c r="B28" s="573" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C28" s="578" t="inlineStr">
+        <is>
+          <t>敬老の日</t>
+        </is>
+      </c>
+      <c r="D28" s="579" t="inlineStr">
+        <is>
+          <t>休み</t>
+        </is>
+      </c>
+      <c r="E28" s="579" t="n"/>
+      <c r="F28" s="576" t="n"/>
+      <c r="G28" s="576" t="n"/>
+      <c r="H28" s="577" t="n"/>
+      <c r="I28" s="577" t="n"/>
+      <c r="J28" s="577" t="n"/>
+      <c r="K28" s="577" t="n"/>
+      <c r="L28" s="577" t="n"/>
+      <c r="M28" s="577" t="n"/>
+      <c r="N28" s="577" t="n"/>
+      <c r="O28" s="577" t="n"/>
+      <c r="P28" s="577" t="n"/>
+      <c r="Q28" s="577" t="n"/>
+      <c r="R28" s="577" t="n"/>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="461" t="n">
+        <v>22</v>
+      </c>
+      <c r="B29" s="461" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C29" s="428" t="n"/>
+      <c r="D29" s="421" t="inlineStr">
+        <is>
+          <t>～18:00</t>
+        </is>
+      </c>
+      <c r="E29" s="421" t="n"/>
+      <c r="F29" s="310" t="n"/>
+      <c r="G29" s="310" t="n"/>
+    </row>
+    <row r="30" ht="23.4" customHeight="1">
+      <c r="A30" s="573" t="n">
+        <v>23</v>
+      </c>
+      <c r="B30" s="573" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C30" s="574" t="inlineStr">
+        <is>
+          <t>秋分の日</t>
+        </is>
+      </c>
+      <c r="D30" s="575" t="inlineStr">
+        <is>
+          <t>9:00～16:00</t>
+        </is>
+      </c>
+      <c r="E30" s="575" t="n"/>
+      <c r="F30" s="576" t="n"/>
+      <c r="G30" s="576" t="n"/>
+      <c r="H30" s="577" t="n"/>
+      <c r="I30" s="577" t="n"/>
+      <c r="J30" s="577" t="n"/>
+      <c r="K30" s="577" t="n"/>
+      <c r="L30" s="577" t="n"/>
+      <c r="M30" s="577" t="n"/>
+      <c r="N30" s="577" t="n"/>
+      <c r="O30" s="577" t="n"/>
+      <c r="P30" s="577" t="n"/>
+      <c r="Q30" s="577" t="n"/>
+      <c r="R30" s="577" t="n"/>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="461" t="n">
+        <v>24</v>
+      </c>
+      <c r="B31" s="461" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C31" s="427" t="inlineStr">
+        <is>
+          <t>第２回推薦願締切</t>
+        </is>
+      </c>
+      <c r="D31" s="421" t="inlineStr">
+        <is>
+          <t>～18:00</t>
+        </is>
+      </c>
+      <c r="E31" s="420" t="n"/>
+      <c r="F31" s="310" t="n"/>
+      <c r="G31" s="310" t="n"/>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="461" t="n">
+        <v>25</v>
+      </c>
+      <c r="B32" s="461" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C32" s="427" t="inlineStr">
+        <is>
+          <t>生徒会役員選挙活動期間（10/1まで）　SC来校</t>
+        </is>
+      </c>
+      <c r="D32" s="420" t="inlineStr">
+        <is>
+          <t>～18:00</t>
+        </is>
+      </c>
+      <c r="E32" s="420" t="n"/>
+      <c r="F32" s="310" t="n"/>
+      <c r="G32" s="310" t="n"/>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="573" t="n">
+        <v>26</v>
+      </c>
+      <c r="B33" s="573" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C33" s="574" t="n"/>
+      <c r="D33" s="575" t="inlineStr">
+        <is>
+          <t>9:00～16:00</t>
+        </is>
+      </c>
+      <c r="E33" s="575" t="n"/>
+      <c r="F33" s="576" t="n"/>
+      <c r="G33" s="576" t="n"/>
+      <c r="H33" s="577" t="n"/>
+      <c r="I33" s="577" t="n"/>
+      <c r="J33" s="577" t="n"/>
+      <c r="K33" s="577" t="n"/>
+      <c r="L33" s="577" t="n"/>
+      <c r="M33" s="577" t="n"/>
+      <c r="N33" s="577" t="n"/>
+      <c r="O33" s="577" t="n"/>
+      <c r="P33" s="577" t="n"/>
+      <c r="Q33" s="577" t="n"/>
+      <c r="R33" s="577" t="n"/>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="573" t="n">
+        <v>27</v>
+      </c>
+      <c r="B34" s="573" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C34" s="578" t="n"/>
+      <c r="D34" s="579" t="inlineStr">
+        <is>
+          <t>休み</t>
+        </is>
+      </c>
+      <c r="E34" s="579" t="n"/>
+      <c r="F34" s="576" t="n"/>
+      <c r="G34" s="576" t="n"/>
+      <c r="H34" s="577" t="n"/>
+      <c r="I34" s="577" t="n"/>
+      <c r="J34" s="577" t="n"/>
+      <c r="K34" s="577" t="n"/>
+      <c r="L34" s="577" t="n"/>
+      <c r="M34" s="577" t="n"/>
+      <c r="N34" s="577" t="n"/>
+      <c r="O34" s="577" t="n"/>
+      <c r="P34" s="577" t="n"/>
+      <c r="Q34" s="577" t="n"/>
+      <c r="R34" s="577" t="n"/>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="461" t="n">
+        <v>28</v>
+      </c>
+      <c r="B35" s="461" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C35" s="427" t="n"/>
+      <c r="D35" s="420" t="inlineStr">
+        <is>
+          <t>休み</t>
+        </is>
+      </c>
+      <c r="E35" s="420" t="n"/>
+      <c r="F35" s="310" t="n"/>
+      <c r="G35" s="310" t="n"/>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="461" t="n">
+        <v>29</v>
+      </c>
+      <c r="B36" s="461" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C36" s="428" t="inlineStr">
+        <is>
+          <t>第2回推薦会議</t>
+        </is>
+      </c>
+      <c r="D36" s="421" t="inlineStr">
+        <is>
+          <t>～18:00</t>
+        </is>
+      </c>
+      <c r="E36" s="421" t="n"/>
+      <c r="F36" s="310" t="n"/>
+      <c r="G36" s="310" t="n"/>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="461" t="n">
+        <v>30</v>
+      </c>
+      <c r="B37" s="461" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C37" s="428" t="inlineStr">
+        <is>
+          <t>40×6</t>
+        </is>
+      </c>
+      <c r="D37" s="421" t="inlineStr">
+        <is>
+          <t>～18:00</t>
+        </is>
+      </c>
+      <c r="E37" s="421" t="n"/>
+      <c r="F37" s="310" t="n"/>
+      <c r="G37" s="310" t="n"/>
+    </row>
+    <row r="38" ht="24" customHeight="1" thickBot="1">
+      <c r="A38" s="463" t="n"/>
+      <c r="B38" s="461" t="n"/>
+      <c r="C38" s="428" t="n"/>
+      <c r="D38" s="421" t="n"/>
+      <c r="E38" s="421" t="n"/>
+      <c r="F38" s="310" t="n"/>
+      <c r="G38" s="310" t="n"/>
+      <c r="L38" s="1" t="n"/>
+    </row>
+    <row r="39" ht="126.75" customHeight="1" thickBot="1">
+      <c r="A39" s="524" t="inlineStr">
+        <is>
+          <t>ミューザ川崎吹奏楽祭・アンサンブルコンテスト（日程確認要）</t>
+        </is>
+      </c>
+      <c r="B39" s="525" t="n"/>
+      <c r="C39" s="525" t="n"/>
+      <c r="D39" s="525" t="n"/>
+      <c r="E39" s="526" t="n"/>
+      <c r="F39" s="345" t="n"/>
+      <c r="G39" s="345" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.7086614173228347" right="0.7086614173228347" top="0.7480314960629921" bottom="0.7480314960629921" header="0.3149606299212598" footer="0.3149606299212598"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="84" horizontalDpi="4294967294"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="Sheet2">

--- a/2026年度_8月_吹奏楽部活動予定.xlsx
+++ b/2026年度_8月_吹奏楽部活動予定.xlsx
@@ -23499,7 +23499,7 @@
           <t>～18:00</t>
         </is>
       </c>
-      <c r="E8" s="421" t="n"/>
+      <c r="E8" s="421" t="inlineStr"/>
       <c r="F8" s="310" t="inlineStr">
         <is>
           <t>１行  15.75</t>
@@ -23526,7 +23526,7 @@
           <t>～18:00</t>
         </is>
       </c>
-      <c r="E9" s="420" t="n"/>
+      <c r="E9" s="420" t="inlineStr"/>
       <c r="F9" s="310" t="inlineStr">
         <is>
           <t>MSPゴシック１２　日・曜日・行事</t>
@@ -23545,15 +23545,19 @@
       </c>
       <c r="C10" s="427" t="inlineStr">
         <is>
-          <t>40×6</t>
+          <t>文化祭全日準備①</t>
         </is>
       </c>
       <c r="D10" s="420" t="inlineStr">
         <is>
-          <t>～18:00</t>
-        </is>
-      </c>
-      <c r="E10" s="420" t="n"/>
+          <t>リハーサル</t>
+        </is>
+      </c>
+      <c r="E10" s="420" t="inlineStr">
+        <is>
+          <t>おそらく合奏はリハの時間のみしかできない</t>
+        </is>
+      </c>
       <c r="F10" s="310" t="n"/>
       <c r="G10" s="310" t="n"/>
     </row>
@@ -23568,7 +23572,7 @@
       </c>
       <c r="C11" s="427" t="inlineStr">
         <is>
-          <t>文化祭全日準備①　SSW来校</t>
+          <t>文化祭全日準備②　SSW来校</t>
         </is>
       </c>
       <c r="D11" s="420" t="inlineStr">
@@ -23578,7 +23582,7 @@
       </c>
       <c r="E11" s="420" t="inlineStr">
         <is>
-          <t>おそらく合奏はリハの時間のみ</t>
+          <t>おそらく合奏はリハの時間のみしかできない</t>
         </is>
       </c>
       <c r="F11" s="310" t="n"/>
@@ -23603,7 +23607,7 @@
           <t>本番</t>
         </is>
       </c>
-      <c r="E12" s="575" t="n"/>
+      <c r="E12" s="575" t="inlineStr"/>
       <c r="F12" s="585" t="n"/>
       <c r="G12" s="576" t="n"/>
       <c r="H12" s="577" t="n"/>
@@ -23647,7 +23651,7 @@
           <t>本番</t>
         </is>
       </c>
-      <c r="E13" s="579" t="n"/>
+      <c r="E13" s="579" t="inlineStr"/>
       <c r="F13" s="582" t="inlineStr">
         <is>
           <t>筬島　勇貴</t>
@@ -23697,7 +23701,7 @@
           <t>片付け</t>
         </is>
       </c>
-      <c r="E14" s="420" t="n"/>
+      <c r="E14" s="420" t="inlineStr"/>
       <c r="F14" s="581" t="inlineStr">
         <is>
           <t>篠崎　倫也</t>
@@ -23732,90 +23736,102 @@
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="461" t="n">
+      <c r="A15" s="573" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="461" t="inlineStr">
+      <c r="B15" s="573" t="inlineStr">
         <is>
           <t>火</t>
         </is>
       </c>
-      <c r="C15" s="428" t="inlineStr">
+      <c r="C15" s="574" t="inlineStr">
         <is>
           <t>代休</t>
         </is>
       </c>
-      <c r="D15" s="420" t="inlineStr">
+      <c r="D15" s="579" t="inlineStr">
         <is>
           <t>休み</t>
         </is>
       </c>
-      <c r="E15" s="421" t="n"/>
-      <c r="F15" s="581" t="inlineStr">
+      <c r="E15" s="575" t="inlineStr"/>
+      <c r="F15" s="582" t="inlineStr">
         <is>
           <t>市岡　裕次</t>
         </is>
       </c>
-      <c r="G15" s="310" t="n"/>
-      <c r="M15" s="328">
+      <c r="G15" s="576" t="n"/>
+      <c r="H15" s="577" t="n"/>
+      <c r="I15" s="577" t="n"/>
+      <c r="J15" s="577" t="n"/>
+      <c r="K15" s="577" t="n"/>
+      <c r="L15" s="577" t="n"/>
+      <c r="M15" s="583">
         <f>TIME(0,35,0)</f>
         <v/>
       </c>
-      <c r="N15" s="328">
+      <c r="N15" s="583">
         <f>N14+M15</f>
         <v/>
       </c>
-      <c r="P15" s="328">
+      <c r="O15" s="577" t="n"/>
+      <c r="P15" s="583">
         <f>TIME(0,40,0)</f>
         <v/>
       </c>
-      <c r="Q15" s="328">
+      <c r="Q15" s="583">
         <f>Q14+P15</f>
         <v/>
       </c>
+      <c r="R15" s="577" t="n"/>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="461" t="n">
+      <c r="A16" s="573" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="461" t="inlineStr">
+      <c r="B16" s="573" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
-      <c r="C16" s="428" t="inlineStr">
+      <c r="C16" s="574" t="inlineStr">
         <is>
           <t>代休</t>
         </is>
       </c>
-      <c r="D16" s="420" t="inlineStr">
+      <c r="D16" s="579" t="inlineStr">
         <is>
           <t>休み</t>
         </is>
       </c>
-      <c r="E16" s="421" t="n"/>
-      <c r="F16" s="310" t="n"/>
-      <c r="G16" s="310" t="n"/>
-      <c r="M16" s="328">
+      <c r="E16" s="575" t="inlineStr"/>
+      <c r="F16" s="576" t="n"/>
+      <c r="G16" s="576" t="n"/>
+      <c r="H16" s="577" t="n"/>
+      <c r="I16" s="577" t="n"/>
+      <c r="J16" s="577" t="n"/>
+      <c r="K16" s="577" t="n"/>
+      <c r="L16" s="577" t="n"/>
+      <c r="M16" s="583">
         <f>TIME(0,10,0)</f>
         <v/>
       </c>
-      <c r="N16" s="328">
+      <c r="N16" s="583">
         <f>N15+M16</f>
         <v/>
       </c>
-      <c r="O16" s="1" t="n">
+      <c r="O16" s="584" t="n">
         <v>3</v>
       </c>
-      <c r="P16" s="328">
+      <c r="P16" s="583">
         <f>TIME(0,10,0)</f>
         <v/>
       </c>
-      <c r="Q16" s="328">
+      <c r="Q16" s="583">
         <f>Q15+P16</f>
         <v/>
       </c>
-      <c r="R16" s="1" t="n">
+      <c r="R16" s="584" t="n">
         <v>3</v>
       </c>
     </row>
@@ -23838,7 +23854,7 @@
           <t>～18:00</t>
         </is>
       </c>
-      <c r="E17" s="421" t="n"/>
+      <c r="E17" s="421" t="inlineStr"/>
       <c r="F17" s="310" t="n"/>
       <c r="G17" s="310" t="n"/>
       <c r="M17" s="328">
@@ -23877,7 +23893,7 @@
           <t>～18:00</t>
         </is>
       </c>
-      <c r="E18" s="420" t="n"/>
+      <c r="E18" s="420" t="inlineStr"/>
       <c r="F18" s="310" t="n"/>
       <c r="G18" s="310" t="n"/>
       <c r="M18" s="328">
@@ -23912,13 +23928,13 @@
           <t>土</t>
         </is>
       </c>
-      <c r="C19" s="574" t="n"/>
+      <c r="C19" s="574" t="inlineStr"/>
       <c r="D19" s="575" t="inlineStr">
         <is>
           <t>9:00～16:00</t>
         </is>
       </c>
-      <c r="E19" s="575" t="n"/>
+      <c r="E19" s="575" t="inlineStr"/>
       <c r="F19" s="576" t="n"/>
       <c r="G19" s="576" t="n"/>
       <c r="H19" s="577" t="n"/>
@@ -23958,13 +23974,13 @@
           <t>日</t>
         </is>
       </c>
-      <c r="C20" s="578" t="n"/>
+      <c r="C20" s="578" t="inlineStr"/>
       <c r="D20" s="579" t="inlineStr">
         <is>
           <t>休み</t>
         </is>
       </c>
-      <c r="E20" s="579" t="n"/>
+      <c r="E20" s="579" t="inlineStr"/>
       <c r="F20" s="576" t="n"/>
       <c r="G20" s="576" t="n"/>
       <c r="H20" s="577" t="n"/>
@@ -24004,13 +24020,13 @@
           <t>月</t>
         </is>
       </c>
-      <c r="C21" s="427" t="n"/>
+      <c r="C21" s="427" t="inlineStr"/>
       <c r="D21" s="420" t="inlineStr">
         <is>
           <t>～18:00</t>
         </is>
       </c>
-      <c r="E21" s="420" t="n"/>
+      <c r="E21" s="420" t="inlineStr"/>
       <c r="F21" s="310" t="n"/>
       <c r="G21" s="310" t="n"/>
       <c r="M21" s="328">
@@ -24039,13 +24055,13 @@
           <t>火</t>
         </is>
       </c>
-      <c r="C22" s="428" t="n"/>
+      <c r="C22" s="428" t="inlineStr"/>
       <c r="D22" s="420" t="inlineStr">
         <is>
           <t>～18:00</t>
         </is>
       </c>
-      <c r="E22" s="421" t="n"/>
+      <c r="E22" s="421" t="inlineStr"/>
       <c r="F22" s="310" t="n"/>
       <c r="G22" s="310" t="n"/>
       <c r="M22" s="328">
@@ -24087,7 +24103,7 @@
           <t>～18:00</t>
         </is>
       </c>
-      <c r="E23" s="421" t="n"/>
+      <c r="E23" s="421" t="inlineStr"/>
       <c r="F23" s="310" t="n"/>
       <c r="G23" s="310" t="n"/>
       <c r="M23" s="328">
@@ -24114,7 +24130,7 @@
       </c>
       <c r="C24" s="427" t="inlineStr">
         <is>
-          <t>40×6　第１回推薦会議②　SC来校</t>
+          <t>40×6　第１回推薦会議②　SC</t>
         </is>
       </c>
       <c r="D24" s="420" t="inlineStr">
@@ -24122,7 +24138,7 @@
           <t>～18:00</t>
         </is>
       </c>
-      <c r="E24" s="420" t="n"/>
+      <c r="E24" s="420" t="inlineStr"/>
       <c r="F24" s="310" t="n"/>
       <c r="G24" s="310" t="n"/>
       <c r="M24" s="328">
@@ -24160,7 +24176,7 @@
           <t>～18:00</t>
         </is>
       </c>
-      <c r="E25" s="420" t="n"/>
+      <c r="E25" s="420" t="inlineStr"/>
       <c r="F25" s="310" t="n"/>
       <c r="G25" s="310" t="n"/>
       <c r="M25" s="328">
@@ -24185,13 +24201,13 @@
           <t>土</t>
         </is>
       </c>
-      <c r="C26" s="574" t="n"/>
+      <c r="C26" s="574" t="inlineStr"/>
       <c r="D26" s="575" t="inlineStr">
         <is>
           <t>9:00～16:00</t>
         </is>
       </c>
-      <c r="E26" s="575" t="n"/>
+      <c r="E26" s="575" t="inlineStr"/>
       <c r="F26" s="576" t="n"/>
       <c r="G26" s="576" t="n"/>
       <c r="H26" s="577" t="n"/>
@@ -24215,13 +24231,13 @@
           <t>日</t>
         </is>
       </c>
-      <c r="C27" s="578" t="n"/>
+      <c r="C27" s="578" t="inlineStr"/>
       <c r="D27" s="579" t="inlineStr">
         <is>
           <t>休み</t>
         </is>
       </c>
-      <c r="E27" s="579" t="n"/>
+      <c r="E27" s="579" t="inlineStr"/>
       <c r="F27" s="576" t="n"/>
       <c r="G27" s="576" t="n"/>
       <c r="H27" s="577" t="n"/>
@@ -24255,7 +24271,7 @@
           <t>休み</t>
         </is>
       </c>
-      <c r="E28" s="579" t="n"/>
+      <c r="E28" s="579" t="inlineStr"/>
       <c r="F28" s="576" t="n"/>
       <c r="G28" s="576" t="n"/>
       <c r="H28" s="577" t="n"/>
@@ -24279,13 +24295,13 @@
           <t>火</t>
         </is>
       </c>
-      <c r="C29" s="428" t="n"/>
+      <c r="C29" s="428" t="inlineStr"/>
       <c r="D29" s="421" t="inlineStr">
         <is>
           <t>～18:00</t>
         </is>
       </c>
-      <c r="E29" s="421" t="n"/>
+      <c r="E29" s="421" t="inlineStr"/>
       <c r="F29" s="310" t="n"/>
       <c r="G29" s="310" t="n"/>
     </row>
@@ -24308,7 +24324,7 @@
           <t>9:00～16:00</t>
         </is>
       </c>
-      <c r="E30" s="575" t="n"/>
+      <c r="E30" s="575" t="inlineStr"/>
       <c r="F30" s="576" t="n"/>
       <c r="G30" s="576" t="n"/>
       <c r="H30" s="577" t="n"/>
@@ -24342,7 +24358,7 @@
           <t>～18:00</t>
         </is>
       </c>
-      <c r="E31" s="420" t="n"/>
+      <c r="E31" s="420" t="inlineStr"/>
       <c r="F31" s="310" t="n"/>
       <c r="G31" s="310" t="n"/>
     </row>
@@ -24365,7 +24381,7 @@
           <t>～18:00</t>
         </is>
       </c>
-      <c r="E32" s="420" t="n"/>
+      <c r="E32" s="420" t="inlineStr"/>
       <c r="F32" s="310" t="n"/>
       <c r="G32" s="310" t="n"/>
     </row>
@@ -24378,13 +24394,17 @@
           <t>土</t>
         </is>
       </c>
-      <c r="C33" s="574" t="n"/>
+      <c r="C33" s="574" t="inlineStr"/>
       <c r="D33" s="575" t="inlineStr">
         <is>
-          <t>9:00～16:00</t>
-        </is>
-      </c>
-      <c r="E33" s="575" t="n"/>
+          <t>本番</t>
+        </is>
+      </c>
+      <c r="E33" s="575" t="inlineStr">
+        <is>
+          <t>ハートフルコンサート（千代ヶ丘小）</t>
+        </is>
+      </c>
       <c r="F33" s="576" t="n"/>
       <c r="G33" s="576" t="n"/>
       <c r="H33" s="577" t="n"/>
@@ -24408,13 +24428,13 @@
           <t>日</t>
         </is>
       </c>
-      <c r="C34" s="578" t="n"/>
+      <c r="C34" s="578" t="inlineStr"/>
       <c r="D34" s="579" t="inlineStr">
         <is>
           <t>休み</t>
         </is>
       </c>
-      <c r="E34" s="579" t="n"/>
+      <c r="E34" s="579" t="inlineStr"/>
       <c r="F34" s="576" t="n"/>
       <c r="G34" s="576" t="n"/>
       <c r="H34" s="577" t="n"/>
@@ -24438,13 +24458,13 @@
           <t>月</t>
         </is>
       </c>
-      <c r="C35" s="427" t="n"/>
+      <c r="C35" s="427" t="inlineStr"/>
       <c r="D35" s="420" t="inlineStr">
         <is>
           <t>休み</t>
         </is>
       </c>
-      <c r="E35" s="420" t="n"/>
+      <c r="E35" s="420" t="inlineStr"/>
       <c r="F35" s="310" t="n"/>
       <c r="G35" s="310" t="n"/>
     </row>
@@ -24467,7 +24487,7 @@
           <t>～18:00</t>
         </is>
       </c>
-      <c r="E36" s="421" t="n"/>
+      <c r="E36" s="421" t="inlineStr"/>
       <c r="F36" s="310" t="n"/>
       <c r="G36" s="310" t="n"/>
     </row>
@@ -24480,17 +24500,13 @@
           <t>水</t>
         </is>
       </c>
-      <c r="C37" s="428" t="inlineStr">
-        <is>
-          <t>40×6</t>
-        </is>
-      </c>
+      <c r="C37" s="428" t="inlineStr"/>
       <c r="D37" s="421" t="inlineStr">
         <is>
           <t>～18:00</t>
         </is>
       </c>
-      <c r="E37" s="421" t="n"/>
+      <c r="E37" s="421" t="inlineStr"/>
       <c r="F37" s="310" t="n"/>
       <c r="G37" s="310" t="n"/>
     </row>
